--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_RESTAURANTE LOS ARCOS CB SOLARES.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_RESTAURANTE LOS ARCOS CB SOLARES.xlsx
@@ -565,13 +565,13 @@
         <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>82.4328</v>
+        <v>70.9567</v>
       </c>
       <c r="E2" t="n">
-        <v>57.4856</v>
+        <v>50.0853</v>
       </c>
       <c r="F2" t="n">
-        <v>24.9471</v>
+        <v>20.8717</v>
       </c>
       <c r="G2" t="n">
         <v>56.3528</v>
@@ -610,13 +610,13 @@
         <v>59.2535</v>
       </c>
       <c r="S2" t="n">
-        <v>19.6181</v>
+        <v>8.141999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>10.8622</v>
+        <v>3.4619</v>
       </c>
       <c r="U2" t="n">
-        <v>8.7559</v>
+        <v>4.68</v>
       </c>
       <c r="V2" t="n">
         <v>-7.820800000000001</v>
@@ -643,13 +643,13 @@
         <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>38.1784</v>
+        <v>46.7424</v>
       </c>
       <c r="E3" t="n">
-        <v>8.925099999999999</v>
+        <v>15.2188</v>
       </c>
       <c r="F3" t="n">
-        <v>29.2535</v>
+        <v>31.5231</v>
       </c>
       <c r="G3" t="n">
         <v>4.317100000000001</v>
@@ -688,13 +688,13 @@
         <v>62.3415</v>
       </c>
       <c r="S3" t="n">
-        <v>-11.459</v>
+        <v>-2.8954</v>
       </c>
       <c r="T3" t="n">
-        <v>-9.110099999999999</v>
+        <v>-2.8163</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.3485</v>
+        <v>-0.07899999999999972</v>
       </c>
       <c r="V3" t="n">
         <v>10.3857</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. MARTINEZ FERNANDEZ</t>
+          <t>L. MAESTRO STEELE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>14.9642</v>
+        <v>8.954799999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.784700000000002</v>
+        <v>0.1195999999999998</v>
       </c>
       <c r="F4" t="n">
-        <v>18.7487</v>
+        <v>8.835099999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>-12.9045</v>
+        <v>5.3695</v>
       </c>
       <c r="H4" t="n">
-        <v>-17.2075</v>
+        <v>5.6608</v>
       </c>
       <c r="I4" t="n">
-        <v>4.3026</v>
+        <v>-0.2912000000000003</v>
       </c>
       <c r="J4" t="n">
-        <v>5.244800000000001</v>
+        <v>17.9951</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.257100000000001</v>
+        <v>12.1076</v>
       </c>
       <c r="L4" t="n">
-        <v>12.5021</v>
+        <v>5.8874</v>
       </c>
       <c r="M4" t="n">
-        <v>-18.1493</v>
+        <v>-12.6257</v>
       </c>
       <c r="N4" t="n">
-        <v>-9.9504</v>
+        <v>-6.447</v>
       </c>
       <c r="O4" t="n">
-        <v>-8.1989</v>
+        <v>-6.178599999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>12.3524</v>
+        <v>11.1945</v>
       </c>
       <c r="Q4" t="n">
-        <v>-50.5676</v>
+        <v>-15.0544</v>
       </c>
       <c r="R4" t="n">
-        <v>62.9206</v>
+        <v>26.2492</v>
       </c>
       <c r="S4" t="n">
-        <v>22.0891</v>
+        <v>-0.6623000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>23.0643</v>
+        <v>-3.6359</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9754999999999998</v>
+        <v>2.9738</v>
       </c>
       <c r="V4" t="n">
-        <v>-6.5733</v>
+        <v>-6.9469</v>
       </c>
       <c r="W4" t="n">
-        <v>18.4747</v>
+        <v>0.8154</v>
       </c>
       <c r="X4" t="n">
-        <v>-25.0479</v>
+        <v>-7.762300000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. MAESTRO STEELE</t>
+          <t>S. MARTINEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>2.488299999999999</v>
+        <v>0.5761999999999987</v>
       </c>
       <c r="E5" t="n">
-        <v>-4.261500000000002</v>
+        <v>-20.6014</v>
       </c>
       <c r="F5" t="n">
-        <v>6.749899999999999</v>
+        <v>21.1775</v>
       </c>
       <c r="G5" t="n">
-        <v>5.3695</v>
+        <v>-12.9045</v>
       </c>
       <c r="H5" t="n">
-        <v>5.6608</v>
+        <v>-17.2075</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2912000000000003</v>
+        <v>4.3026</v>
       </c>
       <c r="J5" t="n">
-        <v>17.9951</v>
+        <v>5.244800000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>12.1076</v>
+        <v>-7.257100000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>5.8874</v>
+        <v>12.5021</v>
       </c>
       <c r="M5" t="n">
-        <v>-12.6257</v>
+        <v>-18.1493</v>
       </c>
       <c r="N5" t="n">
-        <v>-6.447</v>
+        <v>-9.9504</v>
       </c>
       <c r="O5" t="n">
-        <v>-6.178599999999999</v>
+        <v>-8.1989</v>
       </c>
       <c r="P5" t="n">
-        <v>11.1945</v>
+        <v>12.3524</v>
       </c>
       <c r="Q5" t="n">
-        <v>-15.0544</v>
+        <v>-50.5676</v>
       </c>
       <c r="R5" t="n">
-        <v>26.2492</v>
+        <v>62.9206</v>
       </c>
       <c r="S5" t="n">
-        <v>-7.1288</v>
+        <v>7.7013</v>
       </c>
       <c r="T5" t="n">
-        <v>-8.017300000000001</v>
+        <v>6.2476</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8886999999999999</v>
+        <v>1.454</v>
       </c>
       <c r="V5" t="n">
-        <v>-6.9469</v>
+        <v>-6.5733</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8154</v>
+        <v>18.4747</v>
       </c>
       <c r="X5" t="n">
-        <v>-7.762300000000001</v>
+        <v>-25.0479</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.130299999999999</v>
+        <v>-0.2168000000000008</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.9065</v>
+        <v>-6.9344</v>
       </c>
       <c r="F6" t="n">
-        <v>3.7761</v>
+        <v>6.7172</v>
       </c>
       <c r="G6" t="n">
         <v>-13.3914</v>
@@ -922,13 +922,13 @@
         <v>21.8094</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4192</v>
+        <v>2.3325</v>
       </c>
       <c r="T6" t="n">
-        <v>5.6215</v>
+        <v>3.5937</v>
       </c>
       <c r="U6" t="n">
-        <v>-4.2021</v>
+        <v>-1.2612</v>
       </c>
       <c r="V6" t="n">
         <v>6.0164</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. SANCHEZ MARROYO</t>
+          <t>D. CONTRERAS MARTINEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>-7.5968</v>
+        <v>-1.8664</v>
       </c>
       <c r="E7" t="n">
-        <v>-7.930400000000001</v>
+        <v>-21.0492</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3335999999999999</v>
+        <v>19.1827</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.9774</v>
+        <v>0.4218000000000002</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9643999999999999</v>
+        <v>2.6492</v>
       </c>
       <c r="I7" t="n">
-        <v>-4.013</v>
+        <v>-2.2277</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.8504</v>
+        <v>20.4852</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.6044</v>
+        <v>11.8049</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2459</v>
+        <v>8.680299999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1269</v>
+        <v>-20.0632</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6401000000000001</v>
+        <v>-9.1554</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.7671</v>
+        <v>-10.9075</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3860000000000001</v>
+        <v>2.702</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.0181</v>
+        <v>-57.9021</v>
       </c>
       <c r="R7" t="n">
-        <v>4.6322</v>
+        <v>60.6047</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3993</v>
+        <v>-3.0014</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3475999999999999</v>
+        <v>-2.5836</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0518</v>
+        <v>-0.4176000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8342000000000001</v>
+        <v>-1.9891</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2859</v>
+        <v>18.9518</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1201</v>
+        <v>-20.941</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. CONTRERAS MARTINEZ</t>
+          <t>J. SANCHEZ MARROYO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>-9.436299999999999</v>
+        <v>-6.367699999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-25.6814</v>
+        <v>-7.6112</v>
       </c>
       <c r="F8" t="n">
-        <v>16.2449</v>
+        <v>1.2436</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4218000000000002</v>
+        <v>-4.9774</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6492</v>
+        <v>-0.9643999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.2277</v>
+        <v>-4.013</v>
       </c>
       <c r="J8" t="n">
-        <v>20.4852</v>
+        <v>-2.8504</v>
       </c>
       <c r="K8" t="n">
-        <v>11.8049</v>
+        <v>-1.6044</v>
       </c>
       <c r="L8" t="n">
-        <v>8.680299999999999</v>
+        <v>-1.2459</v>
       </c>
       <c r="M8" t="n">
-        <v>-20.0632</v>
+        <v>-2.1269</v>
       </c>
       <c r="N8" t="n">
-        <v>-9.1554</v>
+        <v>0.6401000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-10.9075</v>
+        <v>-2.7671</v>
       </c>
       <c r="P8" t="n">
-        <v>2.702</v>
+        <v>-0.3860000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-57.9021</v>
+        <v>-5.0181</v>
       </c>
       <c r="R8" t="n">
-        <v>60.6047</v>
+        <v>4.6322</v>
       </c>
       <c r="S8" t="n">
-        <v>-10.571</v>
+        <v>-0.1701999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-7.2157</v>
+        <v>-0.02839999999999998</v>
       </c>
       <c r="U8" t="n">
-        <v>-3.3555</v>
+        <v>-0.1419</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.9891</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>18.9518</v>
+        <v>0.2859</v>
       </c>
       <c r="X8" t="n">
-        <v>-20.941</v>
+        <v>-1.1201</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>-13.1514</v>
+        <v>-16.5052</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.791399999999999</v>
+        <v>-8.7423</v>
       </c>
       <c r="F9" t="n">
-        <v>-7.3601</v>
+        <v>-7.7631</v>
       </c>
       <c r="G9" t="n">
         <v>-9.1387</v>
@@ -1156,13 +1156,13 @@
         <v>17.3703</v>
       </c>
       <c r="S9" t="n">
-        <v>5.8331</v>
+        <v>2.4797</v>
       </c>
       <c r="T9" t="n">
-        <v>7.109999999999999</v>
+        <v>4.1591</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.2768</v>
+        <v>-1.6796</v>
       </c>
       <c r="V9" t="n">
         <v>-11.5834</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. UGARTE JAUREGUI</t>
+          <t>E. GANDARILLAS GARMENDIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D10" t="n">
-        <v>-19.974</v>
+        <v>-17.0384</v>
       </c>
       <c r="E10" t="n">
-        <v>-14.4101</v>
+        <v>-26.1967</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.5641</v>
+        <v>9.158300000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-13.0195</v>
+        <v>-9.8725</v>
       </c>
       <c r="H10" t="n">
-        <v>-5.8121</v>
+        <v>-7.5034</v>
       </c>
       <c r="I10" t="n">
-        <v>-7.2074</v>
+        <v>-2.3694</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5335</v>
+        <v>4.5528</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5546000000000003</v>
+        <v>2.6111</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.9788000000000002</v>
+        <v>1.9417</v>
       </c>
       <c r="M10" t="n">
-        <v>-11.486</v>
+        <v>-14.425</v>
       </c>
       <c r="N10" t="n">
-        <v>-5.2575</v>
+        <v>-10.1142</v>
       </c>
       <c r="O10" t="n">
-        <v>-6.2286</v>
+        <v>-4.3109</v>
       </c>
       <c r="P10" t="n">
-        <v>7.7201</v>
+        <v>-0.5791000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-14.2826</v>
+        <v>-42.0756</v>
       </c>
       <c r="R10" t="n">
-        <v>22.0027</v>
+        <v>41.4968</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4831999999999999</v>
+        <v>-3.2972</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2046</v>
+        <v>-1.5475</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.6878</v>
+        <v>-1.7498</v>
       </c>
       <c r="V10" t="n">
-        <v>-14.1916</v>
+        <v>-3.289400000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2015</v>
+        <v>12.8741</v>
       </c>
       <c r="X10" t="n">
-        <v>-14.3931</v>
+        <v>-16.1637</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. GANDARILLAS GARMENDIA</t>
+          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>-30.0275</v>
+        <v>-17.2542</v>
       </c>
       <c r="E11" t="n">
-        <v>-35.4414</v>
+        <v>-32.2442</v>
       </c>
       <c r="F11" t="n">
-        <v>5.414000000000001</v>
+        <v>14.9903</v>
       </c>
       <c r="G11" t="n">
-        <v>-9.8725</v>
+        <v>6.952500000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-7.5034</v>
+        <v>25.4779</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.3694</v>
+        <v>-18.525</v>
       </c>
       <c r="J11" t="n">
-        <v>4.5528</v>
+        <v>21.0466</v>
       </c>
       <c r="K11" t="n">
-        <v>2.6111</v>
+        <v>35.5007</v>
       </c>
       <c r="L11" t="n">
-        <v>1.9417</v>
+        <v>-14.4541</v>
       </c>
       <c r="M11" t="n">
-        <v>-14.425</v>
+        <v>-14.094</v>
       </c>
       <c r="N11" t="n">
-        <v>-10.1142</v>
+        <v>-10.0229</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.3109</v>
+        <v>-4.0711</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5791000000000001</v>
+        <v>-22.3888</v>
       </c>
       <c r="Q11" t="n">
-        <v>-42.0756</v>
+        <v>-82.41449999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>41.4968</v>
+        <v>60.0255</v>
       </c>
       <c r="S11" t="n">
-        <v>-16.2858</v>
+        <v>-4.902</v>
       </c>
       <c r="T11" t="n">
-        <v>-10.7922</v>
+        <v>-4.9962</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.4941</v>
+        <v>0.09440000000000032</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.289400000000001</v>
+        <v>3.0846</v>
       </c>
       <c r="W11" t="n">
-        <v>12.8741</v>
+        <v>34.1197</v>
       </c>
       <c r="X11" t="n">
-        <v>-16.1637</v>
+        <v>-31.0356</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
+          <t>J. UGARTE JAUREGUI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>-34.6116</v>
+        <v>-18.6436</v>
       </c>
       <c r="E12" t="n">
-        <v>-44.7093</v>
+        <v>-13.6933</v>
       </c>
       <c r="F12" t="n">
-        <v>10.0978</v>
+        <v>-4.9501</v>
       </c>
       <c r="G12" t="n">
-        <v>6.952500000000001</v>
+        <v>-13.0195</v>
       </c>
       <c r="H12" t="n">
-        <v>25.4779</v>
+        <v>-5.8121</v>
       </c>
       <c r="I12" t="n">
-        <v>-18.525</v>
+        <v>-7.2074</v>
       </c>
       <c r="J12" t="n">
-        <v>21.0466</v>
+        <v>-1.5335</v>
       </c>
       <c r="K12" t="n">
-        <v>35.5007</v>
+        <v>-0.5546000000000003</v>
       </c>
       <c r="L12" t="n">
-        <v>-14.4541</v>
+        <v>-0.9788000000000002</v>
       </c>
       <c r="M12" t="n">
-        <v>-14.094</v>
+        <v>-11.486</v>
       </c>
       <c r="N12" t="n">
-        <v>-10.0229</v>
+        <v>-5.2575</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.0711</v>
+        <v>-6.2286</v>
       </c>
       <c r="P12" t="n">
-        <v>-22.3888</v>
+        <v>7.7201</v>
       </c>
       <c r="Q12" t="n">
-        <v>-82.41449999999999</v>
+        <v>-14.2826</v>
       </c>
       <c r="R12" t="n">
-        <v>60.0255</v>
+        <v>22.0027</v>
       </c>
       <c r="S12" t="n">
-        <v>-22.2594</v>
+        <v>0.8474999999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>-17.4613</v>
+        <v>1.9213</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.7983</v>
+        <v>-1.0741</v>
       </c>
       <c r="V12" t="n">
-        <v>3.0846</v>
+        <v>-14.1916</v>
       </c>
       <c r="W12" t="n">
-        <v>34.1197</v>
+        <v>0.2015</v>
       </c>
       <c r="X12" t="n">
-        <v>-31.0356</v>
+        <v>-14.3931</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>-42.9807</v>
+        <v>-39.077</v>
       </c>
       <c r="E13" t="n">
-        <v>-49.2874</v>
+        <v>-47.7347</v>
       </c>
       <c r="F13" t="n">
-        <v>6.3067</v>
+        <v>8.657400000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-20.877</v>
@@ -1468,13 +1468,13 @@
         <v>51.5333</v>
       </c>
       <c r="S13" t="n">
-        <v>-8.5618</v>
+        <v>-4.658300000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.4074</v>
+        <v>-3.855</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.154300000000001</v>
+        <v>-0.8035</v>
       </c>
       <c r="V13" t="n">
         <v>-19.5255</v>
@@ -1501,13 +1501,13 @@
         <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>-20.84490000000002</v>
+        <v>10.26080000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-129.7934</v>
+        <v>-119.3837</v>
       </c>
       <c r="F14" t="n">
-        <v>108.9481</v>
+        <v>129.6437</v>
       </c>
       <c r="G14" t="n">
         <v>-10.7673</v>
@@ -1516,7 +1516,7 @@
         <v>65.64449999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-76.41220000000001</v>
+        <v>-76.4122</v>
       </c>
       <c r="J14" t="n">
         <v>146.2677</v>
@@ -1525,13 +1525,13 @@
         <v>151.0082</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.739900000000001</v>
+        <v>-4.7399</v>
       </c>
       <c r="M14" t="n">
         <v>-157.0334</v>
       </c>
       <c r="N14" t="n">
-        <v>-85.36370000000001</v>
+        <v>-85.36369999999998</v>
       </c>
       <c r="O14" t="n">
         <v>-71.66990000000001</v>
@@ -1546,13 +1546,13 @@
         <v>490.2397</v>
       </c>
       <c r="S14" t="n">
-        <v>-29.1888</v>
+        <v>1.916199999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-10.489</v>
+        <v>-0.07929999999999948</v>
       </c>
       <c r="U14" t="n">
-        <v>-18.7001</v>
+        <v>1.9955</v>
       </c>
       <c r="V14" t="n">
         <v>-53.26750000000001</v>
